--- a/data/evaluation_results_9.xlsx
+++ b/data/evaluation_results_9.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Metadata" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Runs'!$A$1:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Runs'!$A$1:$J$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Prompts'!$A$1:$B$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Scores'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Scores'!$A$1:$B$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Metadata'!$A$1:$B$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -439,11 +439,10 @@
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,25 +478,20 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ttft_seconds</t>
+          <t>total_latency_seconds</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>total_latency_seconds</t>
+          <t>input_tokens</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>input_tokens</t>
+          <t>output_tokens</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>output_tokens</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>error</t>
         </is>
@@ -524,35 +518,32 @@
         <is>
           <t>To answer this question, we need to consider the following assumptions:
 1. The school has a uniform policy in place.
-2. The student was caught wearing a non-uniform item.
-3. The school administration is consistent in enforcing the uniform policy.
-4. The student's actions were intentional and not a result of forgetfulness or a misunderstanding.
-Based on these assumptions, the most likely consequence for the student would be:
-* Detention or a warning from the teacher or school administrator.
-* A parent contact or meeting to discuss the incident and the student's understanding of the uniform policy.
-* Possible loss of privileges, such as recess or extracurricular activities.
-* In severe cases, the student may face disciplinary action, such as a suspension or detention.
-It's worth noting that the specific consequence would depend on the school's policies and the student's prior behavior. Additionally, the school's approach to enforcing the uniform policy may vary depending on the school's culture and values.</t>
+2. The student is aware of the uniform policy and its expectations.
+3. The student intentionally wore non-uniform clothing.
+4. The school has a system in place for enforcing the uniform policy.
+With these assumptions in mind, the most likely consequence for the student is:
+* Detention or suspension from school
+* Loss of privileges (e.g., participation in extracurricular activities)
+* Parental contact or meeting to discuss the infraction
+* Possible disciplinary action, such as a warning or a written warning
+It's worth noting that the specific consequence may vary depending on the school's policies, the student's age, and the severity of the infraction. However, in general, wearing non-uniform clothing to school is considered a breach of school rules and can result in disciplinary action.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:04:34.827453+00:00</t>
+          <t>2026-10-22T04:47:27.044572+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1.774587906999841</v>
+        <v>1.768423050000024</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1.803999127999987</v>
+        <v>78</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>197</v>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
+        <v>186</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -573,37 +564,34 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>To answer this question, we need to consider the following assumptions:
-1. **The school has a uniform policy**: This assumption is crucial, as it provides the context for the scenario. If the school doesn't have a uniform policy, the student wouldn't be caught wearing a non-uniform.
-2. **The school enforces the uniform policy**: This assumption is also important, as it implies that the school takes the uniform policy seriously and has a system in place to monitor and enforce it.
-3. **The student intentionally wore a non-uniform**: This assumption is necessary to determine the student's intent and the likelihood of consequences. If the student genuinely forgot or didn't know about the uniform policy, the consequences might be different.
-4. **The school's response to non-compliance is consistent**: This assumption helps to determine the severity of the consequences. If the school's response to non-compliance is inconsistent or lenient, the consequences might be less severe.
-With these assumptions in mind, the most likely consequence for the student who is caught wearing a non-uniform would be:
-* Detention or a warning
-* A verbal or written warning from the teacher or school administrator
-* A temporary or permanent removal from extracurricular activities or privileges
-* A parent-teacher conference to discuss the issue and potential consequences
-It's worth noting that the specific consequences would depend on the school's policies, the student's age, and the severity of the infraction.</t>
+          <t>To answer this question, we need to make some assumptions. Here are a few:
+1. The school has a clear policy on uniform enforcement, and the student has been caught violating this policy.
+2. The school administration is consistent in enforcing the uniform policy, and the student's infraction is not a one-time mistake.
+3. The student's infraction is not a result of a legitimate exception or accommodation (e.g., a medical condition that requires a specific type of clothing).
+4. The school's disciplinary policies are fair and reasonable.
+With these assumptions in mind, the most likely consequence for the student is:
+* Detention or a warning, followed by a meeting with the student and/or their parents to discuss the infraction and the importance of adhering to the uniform policy.
+* Possible loss of privileges, such as recess or extracurricular activities, for a specified period.
+* A written warning or a formal disciplinary notice, which may be placed in the student's file.
+* In severe cases, the student may face more serious consequences, such as suspension or expulsion, depending on the school's policies and the severity of the infraction.
+It's worth noting that the specific consequences will depend on the school's policies and the student's individual circumstances.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:04:36.631847+00:00</t>
+          <t>2026-10-22T04:47:28.813427+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>2.571261806999928</v>
+        <v>2.413715593000006</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>2.609711183999934</v>
+        <v>78</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>297</v>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
+        <v>255</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -625,36 +613,29 @@
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>To answer this question, we need to consider the following assumptions:
-1. The school has a uniform policy in place.
-2. The student is aware of the uniform policy and its expectations.
-3. The student intentionally wore a non-uniform item.
-4. The school has a system in place for enforcing the uniform policy (e.g., monitoring students, issuing warnings, etc.).
-Based on these assumptions, the most likely consequence for the student would be:
-* Detention or a warning from the teacher or school administrator.
-* A parent contact or meeting to discuss the infraction and the student's understanding of the uniform policy.
-* Possible loss of privileges, such as recess or extracurricular activities.
-* In severe cases, the student may face disciplinary action, such as a suspension or detention.
-It's worth noting that the specific consequence would depend on the school's policies, the student's age, and the severity of the infraction.</t>
+1. **The school has a uniform policy**: This assumption is crucial, as it provides the context for the student's infraction.
+2. **The student intentionally wore a non-uniform**: This assumption is also important, as it implies that the student deliberately chose not to follow the school's uniform policy.
+3. **The school has a system in place for enforcing the uniform policy**: This assumption is necessary, as it suggests that the school has a way to detect and address non-compliance with the uniform policy.
+With these assumptions in mind, the most likely consequence for the student who is caught wearing a non-uniform is:
+**Detention or disciplinary action**: Many schools have a system in place for enforcing their uniform policy, which may include detention, suspension, or other disciplinary actions for students who fail to comply. The specific consequence will depend on the school's policies and procedures.
+It's worth noting that the consequences may vary depending on the school's policies and the student's prior record. Additionally, some schools may have more lenient or flexible policies regarding uniform enforcement, which could result in a less severe consequence.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:04:39.242208+00:00</t>
+          <t>2026-10-22T04:47:31.227603+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1.784689430999833</v>
+        <v>2.260669429000018</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1.820802070999889</v>
+        <v>78</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>190</v>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
+        <v>239</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -690,22 +671,19 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:04:41.063411+00:00</t>
+          <t>2026-10-22T04:47:33.488746+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1.422777964000034</v>
+        <v>1.468111038000075</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1.440744486000085</v>
+        <v>75</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="J5" s="2" t="n">
         <v>153</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -741,22 +719,19 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:04:42.504381+00:00</t>
+          <t>2026-10-22T04:47:34.957071+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1.423962265</v>
+        <v>1.423480057000006</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1.440742361000048</v>
+        <v>75</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="J6" s="2" t="n">
         <v>153</v>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -777,8 +752,9 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>To solve this problem, we need to make a few assumptions. Let's assume that the cost of the ball is x dollars. Since the bat costs $1.00 more than the ball, the cost of the bat is x + $1.00.
-We know that the total cost of the bat and the ball together is $1.10. We can set up an equation to represent this:
+          <t>To solve this problem, we need to make a few assumptions. Let's assume that the cost of the ball is x dollars.
+Since the bat costs $1.00 more than the ball, the cost of the bat is x + $1.00.
+The total cost of the bat and the ball together is $1.10, so we can set up the equation:
 x + (x + $1.00) = $1.10
 Combine like terms:
 2x + $1.00 = $1.10
@@ -791,22 +767,19 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:04:43.945323+00:00</t>
+          <t>2026-10-22T04:47:36.380790+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1.899709393999956</v>
+        <v>1.358450218999906</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1.918275613999867</v>
+        <v>75</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>158</v>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
+        <v>153</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -833,30 +806,28 @@
 Day 2: The snail climbs 3 feet, so it's at 4 feet. At night, it slips back 2 feet, so it's at 2 feet.
 Day 3: The snail climbs 3 feet, so it's at 5 feet. At night, it slips back 2 feet, so it's at 3 feet.
 Notice a pattern? The snail effectively climbs 1 foot per day (3 feet up, 2 feet back).
-Since the well is 20 feet deep, we can calculate the number of days it takes for the snail to reach the top:
-20 feet (well depth) / 1 foot (effective daily progress) = 20 days
-However, this calculation assumes that the snail will climb the final 3 feet on the 20th day. Since the snail climbs 3 feet on the 20th day, it will reach the top of the well on the 20th day.
-Therefore, it will take the snail 20 days to reach the top of the well.</t>
+Since the well is 20 feet deep, the snail needs to climb 19 feet (20 - 1 foot, since it starts at 1 foot).
+To find the number of days, we can divide the total distance (19 feet) by the snail's daily progress (1 foot):
+19 feet / 1 foot/day = 19 days
+However, this calculation assumes that the snail will climb the final 1 foot on the 19th day. But, since the snail climbs 3 feet on the 19th day, it will actually reach the top of the well on the 19th day.
+Therefore, it will take the snail 19 days to reach the top of the well.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:04:45.863811+00:00</t>
+          <t>2026-10-22T04:47:37.739468+00:00</t>
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>2.615092898000057</v>
+        <v>2.728965648999974</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>2.640667799000084</v>
+        <v>97</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>292</v>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
+        <v>321</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -877,85 +848,85 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>To solve this problem, let's analyze the snail's movement:
+* The snail climbs 3 feet up during the day.
+* At night, it slips back 2 feet, so it effectively moves 1 foot up (3 - 2 = 1).
+Since the well is 20 feet deep, we need to find the number of days it takes for the snail to climb 19 feet (since it will reach the top on the 20th foot).
+Let's calculate the number of days:
+Day 1: 3 feet up, 2 feet back (net progress: 1 foot)
+Day 2: 3 feet up, 2 feet back (net progress: 1 foot)
+...
+Day 19: 3 feet up, 2 feet back (net progress: 1 foot)
+On the 20th day, the snail will climb 3 feet up and reach the top of the well.
+Therefore, it will take the snail 20 days to reach the top of the well.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:47:40.468661+00:00</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>1.916503495000029</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>213</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>A snail is at the bottom of a 20-foot well. Each day, it climbs up 3 feet, but at night, it slips back 2 feet. How many days will it take for the snail to reach the top of the well?</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>To solve this problem, we need to consider the snail's daily progress and the fact that it slips back 2 feet at night.
-Let's break down the snail's progress:
+Let's break it down:
 Day 1: The snail climbs 3 feet, so it's at 3 feet. At night, it slips back 2 feet, so it's at 1 foot.
 Day 2: The snail climbs 3 feet, so it's at 4 feet. At night, it slips back 2 feet, so it's at 2 feet.
 Day 3: The snail climbs 3 feet, so it's at 5 feet. At night, it slips back 2 feet, so it's at 3 feet.
 Notice a pattern? The snail effectively climbs 1 foot per day (3 feet up, 2 feet back).
-Since the well is 20 feet deep, the snail needs to climb 19 feet to reach the top (20 - 1 = 19, since it starts at 1 foot).
-To climb 19 feet at a rate of 1 foot per day, the snail will need 19 days.
-Therefore, it will take the snail 19 days to reach the top of the well.</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21T18:04:48.504714+00:00</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>2.265660500999957</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>2.299165379999977</v>
-      </c>
-      <c r="I9" s="2" t="n">
+Since the well is 20 feet deep, the snail needs to climb 19 feet (20 - 1 foot, since it starts at 1 foot).
+To find the number of days, we can divide the total distance (19 feet) by the snail's daily progress (1 foot):
+19 feet / 1 foot/day = 19 days
+However, this calculation assumes that the snail will climb the final 1 foot on the 19th day. But, on the 19th day, the snail will climb 3 feet, and then it will be at the top of the well (20 feet).
+So, the correct answer is 18 days + 1 day (the final day when the snail climbs the last 1 foot).</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:47:42.385373+00:00</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>2.772411561000013</v>
+      </c>
+      <c r="H10" s="2" t="n">
         <v>97</v>
       </c>
-      <c r="J9" s="2" t="n">
-        <v>259</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>A snail is at the bottom of a 20-foot well. Each day, it climbs up 3 feet, but at night, it slips back 2 feet. How many days will it take for the snail to reach the top of the well?</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>To solve this problem, let's break it down step by step.
-The snail climbs 3 feet up during the day and slips back 2 feet at night, so it effectively moves 1 foot up the well each day.
-Since the well is 20 feet deep, the snail needs to cover 20 feet to reach the top.
-To find the number of days it will take for the snail to reach the top, we can divide the total distance (20 feet) by the daily progress (1 foot):
-20 feet / 1 foot per day = 20 days
-However, this calculation assumes that the snail will climb the entire 20 feet on the final day, without slipping back. But since the snail slips back 2 feet at night, it will actually need one more day to reach the top.
-So, the correct answer is 21 days.</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21T18:04:50.804142+00:00</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>1.783411531999946</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>1.805669121999927</v>
-      </c>
       <c r="I10" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>180</v>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+        <v>330</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K10"/>
+  <autoFilter ref="A1:J10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1027,7 +998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1055,10 +1026,12 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>{
-  "median_ttft": 1.7834115319999455,
-  "median_latency": 1.8056691219999266,
-  "correct_frequency": 0.8333333333333334,
-  "misinformation_frequency": 0
+  "median_input": 76,
+  "median_output": 153,
+  "median_latency": 1.716,
+  "correct_frequency": 0.75,
+  "misinformation_frequency": 0,
+  "relevance_frequency": 1
 }</t>
         </is>
       </c>
@@ -1066,45 +1039,65 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>median_ttft</t>
+          <t>median_input</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1.783411531999946</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>median_latency</t>
+          <t>median_output</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.805669121999927</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>correct_frequency</t>
+          <t>median_latency</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.8333333333333334</v>
+        <v>1.716</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>correct_frequency</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>misinformation_frequency</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B7" s="2" t="n">
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>relevance_frequency</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:B8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1142,7 +1135,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T18:04:54.199999+00:00</t>
+          <t>2026-10-22T04:47:46.724323+00:00</t>
         </is>
       </c>
     </row>
